--- a/Assets/Data/Dungeon3011.xlsx
+++ b/Assets/Data/Dungeon3011.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="15">
   <si>
     <t>Id</t>
   </si>
@@ -68,10 +68,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -98,14 +98,6 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -113,9 +105,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -129,6 +136,29 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -136,14 +166,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -157,61 +187,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,10 +203,33 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -248,13 +248,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -266,7 +296,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -278,7 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -290,139 +410,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -433,6 +433,24 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -447,30 +465,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -493,28 +487,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -533,6 +522,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -541,145 +541,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1801,9 +1801,7 @@
       <c r="I12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J12" t="s">
-        <v>12</v>
-      </c>
+      <c r="J12"/>
       <c r="K12" s="1" t="s">
         <v>10</v>
       </c>
@@ -1862,9 +1860,7 @@
       <c r="I13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="J13"/>
       <c r="K13" s="1" t="s">
         <v>10</v>
       </c>
@@ -1921,13 +1917,11 @@
         <v>9</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>9</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="J14"/>
       <c r="K14" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>9</v>
@@ -1982,13 +1976,11 @@
         <v>9</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>9</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="J15"/>
       <c r="K15" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>9</v>
@@ -2043,13 +2035,11 @@
         <v>9</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>9</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="J16"/>
       <c r="K16" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>9</v>

--- a/Assets/Data/Dungeon3011.xlsx
+++ b/Assets/Data/Dungeon3011.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -100,9 +100,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -120,14 +120,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -136,16 +128,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -159,6 +144,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -167,16 +174,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -191,20 +212,28 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -221,46 +250,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -273,7 +273,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -285,7 +303,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -297,37 +351,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -339,103 +363,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -453,7 +387,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,30 +464,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -506,6 +482,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -517,6 +508,24 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -541,26 +550,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -572,145 +572,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -733,12 +733,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -826,169 +826,185 @@
         </row>
         <row r="4">
           <cell r="D4">
-            <v>2010</v>
+            <v>1020</v>
           </cell>
           <cell r="E4" t="str">
-            <v>ダンジョンから出る</v>
+            <v>エンフェリアイベント再生</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>2020</v>
+            <v>2010</v>
           </cell>
           <cell r="E5" t="str">
-            <v>ダンジョン移動</v>
+            <v>ダンジョンから出る</v>
           </cell>
         </row>
         <row r="6">
           <cell r="D6">
-            <v>2021</v>
+            <v>2011</v>
           </cell>
           <cell r="E6" t="str">
-            <v>移動判定なしでダンジョン移動</v>
+            <v>ダンジョンから出る（確認無し）</v>
           </cell>
         </row>
         <row r="7">
           <cell r="D7">
-            <v>2030</v>
+            <v>2020</v>
           </cell>
           <cell r="E7" t="str">
-            <v>ダンジョンクリア</v>
+            <v>ダンジョン移動</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>3010</v>
+            <v>2021</v>
           </cell>
           <cell r="E8" t="str">
-            <v>アーティファクト取得</v>
+            <v>移動判定なしでダンジョン移動</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>3020</v>
+            <v>2030</v>
           </cell>
           <cell r="E9" t="str">
-            <v>アイテム取得</v>
+            <v>ダンジョンクリア</v>
           </cell>
         </row>
         <row r="10">
           <cell r="D10">
-            <v>3030</v>
+            <v>3010</v>
           </cell>
           <cell r="E10" t="str">
-            <v>魔法入手</v>
+            <v>アーティファクト取得</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11">
-            <v>4010</v>
+            <v>3020</v>
           </cell>
           <cell r="E11" t="str">
-            <v>仲間を増やす</v>
+            <v>アイテム取得</v>
           </cell>
         </row>
         <row r="12">
           <cell r="D12">
-            <v>4011</v>
+            <v>3030</v>
           </cell>
           <cell r="E12" t="str">
-            <v>仲間を外す</v>
+            <v>魔法入手</v>
           </cell>
         </row>
         <row r="13">
           <cell r="D13">
-            <v>4020</v>
+            <v>4010</v>
           </cell>
           <cell r="E13" t="str">
-            <v>選択して仲間を増やす</v>
+            <v>仲間を増やす</v>
           </cell>
         </row>
         <row r="14">
           <cell r="D14">
-            <v>5010</v>
+            <v>4011</v>
           </cell>
           <cell r="E14" t="str">
-            <v>強制戦闘</v>
+            <v>仲間を外す</v>
           </cell>
         </row>
         <row r="15">
           <cell r="D15">
-            <v>5020</v>
+            <v>4020</v>
           </cell>
           <cell r="E15" t="str">
-            <v>強制ボス戦闘</v>
+            <v>選択して仲間を増やす</v>
           </cell>
         </row>
         <row r="16">
           <cell r="D16">
-            <v>6010</v>
+            <v>5010</v>
           </cell>
           <cell r="E16" t="str">
-            <v>指定のイベントマスを消す</v>
+            <v>強制戦闘</v>
           </cell>
         </row>
         <row r="17">
           <cell r="D17">
-            <v>6011</v>
+            <v>5020</v>
           </cell>
           <cell r="E17" t="str">
-            <v>指定のイベントマスを表示する</v>
+            <v>強制ボス戦闘</v>
           </cell>
         </row>
         <row r="18">
           <cell r="D18">
-            <v>6020</v>
+            <v>6010</v>
           </cell>
           <cell r="E18" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
+            <v>指定のイベントマスを消す</v>
           </cell>
         </row>
         <row r="19">
           <cell r="D19">
-            <v>6030</v>
+            <v>6011</v>
           </cell>
           <cell r="E19" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
+            <v>指定のイベントマスを表示する</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>7010</v>
+            <v>6020</v>
           </cell>
           <cell r="E20" t="str">
-            <v>ダメージ床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
           </cell>
         </row>
         <row r="21">
           <cell r="D21">
-            <v>7020</v>
+            <v>6030</v>
           </cell>
           <cell r="E21" t="str">
-            <v>怨嗟床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
           </cell>
         </row>
         <row r="22">
           <cell r="D22">
-            <v>7021</v>
+            <v>7010</v>
           </cell>
           <cell r="E22" t="str">
-            <v>怨嗟床解除</v>
+            <v>ダメージ床</v>
           </cell>
         </row>
         <row r="23">
           <cell r="D23">
-            <v>8010</v>
+            <v>7020</v>
           </cell>
           <cell r="E23" t="str">
-            <v>指定リージョンを開示する</v>
+            <v>怨嗟床</v>
           </cell>
         </row>
         <row r="24">
           <cell r="D24">
+            <v>7021</v>
+          </cell>
+          <cell r="E24" t="str">
+            <v>怨嗟床解除</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="D25">
+            <v>8010</v>
+          </cell>
+          <cell r="E25" t="str">
+            <v>指定リージョンを開示する</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="D26">
             <v>9010</v>
           </cell>
-          <cell r="E24" t="str">
+          <cell r="E26" t="str">
             <v>イベント終了明示</v>
           </cell>
         </row>
@@ -5690,6 +5706,9 @@
   <sheetPr/>
   <dimension ref="A1:K8"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="7"/>
+  <cols>
+    <col min="7" max="7" width="29.1818181818182" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
@@ -5879,7 +5898,7 @@
         <v>仲間を外す</v>
       </c>
       <c r="H6">
-        <v>102</v>
+        <v>201</v>
       </c>
       <c r="I6">
         <v>0</v>

--- a/Assets/Data/Dungeon3011.xlsx
+++ b/Assets/Data/Dungeon3011.xlsx
@@ -120,30 +120,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -159,8 +135,37 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -181,6 +186,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -189,8 +209,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -204,63 +256,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -270,6 +270,24 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -285,7 +303,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -297,157 +441,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,17 +482,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -521,20 +515,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -550,16 +541,25 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -572,7 +572,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -581,136 +581,136 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
